--- a/2/RATTRAPAGES/notes.xlsx
+++ b/2/RATTRAPAGES/notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ESIPE\2\RATTRAPAGES\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\ESIPE\2\RATTRAPAGES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E49A84-9C3D-42A9-95E6-A05B7EB8CE8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{142D5006-B1EF-49C3-8399-C7C7C3B2D80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -394,9 +394,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -419,7 +419,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>13.45</v>
       </c>
@@ -443,7 +443,7 @@
         <v>7.8500000000000005</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1.8</v>
       </c>

--- a/2/RATTRAPAGES/notes.xlsx
+++ b/2/RATTRAPAGES/notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ESIPE\2\RATTRAPAGES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768E50DA-416D-4A64-BD02-82347C2FE26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26792A9-B0FD-4F59-BD15-F9DC7626153B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3825" yWindow="3840" windowWidth="21600" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/2/RATTRAPAGES/notes.xlsx
+++ b/2/RATTRAPAGES/notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ESIPE\2\RATTRAPAGES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26792A9-B0FD-4F59-BD15-F9DC7626153B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD432B3-50BA-4FE6-AB5B-32360B7E1096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3825" yWindow="3840" windowWidth="21600" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5100" yWindow="4515" windowWidth="21600" windowHeight="11085" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -495,7 +495,7 @@
         <v>5.68</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E2" s="4">
         <v>10</v>
@@ -505,7 +505,7 @@
       </c>
       <c r="H2">
         <f>SUMPRODUCT(A2:F2,A3:F3)/SUM(A3:F3)</f>
-        <v>7.8821874999999997</v>
+        <v>8.8821875000000006</v>
       </c>
     </row>
     <row r="3" spans="1:8">

--- a/2/RATTRAPAGES/notes.xlsx
+++ b/2/RATTRAPAGES/notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ESIPE\2\RATTRAPAGES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD432B3-50BA-4FE6-AB5B-32360B7E1096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162C6A19-F429-4A18-B89B-162458BAB6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5100" yWindow="4515" windowWidth="21600" windowHeight="11085" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
   <si>
     <t>maths</t>
   </si>
@@ -59,6 +59,30 @@
   </si>
   <si>
     <t>moyenne</t>
+  </si>
+  <si>
+    <t>algo</t>
+  </si>
+  <si>
+    <t>prog res</t>
+  </si>
+  <si>
+    <t>gl</t>
+  </si>
+  <si>
+    <t>ig</t>
+  </si>
+  <si>
+    <t>anglais</t>
+  </si>
+  <si>
+    <t>cc</t>
+  </si>
+  <si>
+    <t>dt</t>
+  </si>
+  <si>
+    <t>ipp</t>
   </si>
 </sst>
 </file>
@@ -455,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="16384" width="9.140625" style="1"/>
@@ -489,7 +513,7 @@
         <v>13.45</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>5.68</v>
@@ -505,12 +529,12 @@
       </c>
       <c r="H2">
         <f>SUMPRODUCT(A2:F2,A3:F3)/SUM(A3:F3)</f>
-        <v>8.8821875000000006</v>
+        <v>10.028395061728396</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="B3">
         <v>1.5</v>
@@ -522,11 +546,163 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="H6" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="4">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>10.89</v>
+      </c>
+      <c r="C7">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>12</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="H7">
+        <f>SUMPRODUCT(A7:D7,A8:D8)/SUM(A8:D8)</f>
+        <v>10.040000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>1.5</v>
+      </c>
+      <c r="D8">
+        <v>1.5</v>
+      </c>
+      <c r="E8"/>
+      <c r="F8"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="4">
+        <v>13.45</v>
+      </c>
+      <c r="B12">
+        <v>3</v>
+      </c>
+      <c r="C12">
+        <v>5.68</v>
+      </c>
+      <c r="D12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13">
+        <v>1.75</v>
+      </c>
+      <c r="B13">
+        <v>1.5</v>
+      </c>
+      <c r="C13">
+        <v>1.5</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="H15" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="4">
+        <v>5.5</v>
+      </c>
+      <c r="B16">
+        <v>16</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16">
+        <v>16</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="H16">
+        <f>SUMPRODUCT(A16:D16,A17:D17)/SUM(A17:D17)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>1.5</v>
+      </c>
+      <c r="B17">
+        <v>0.75</v>
+      </c>
+      <c r="C17">
+        <v>0.75</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17"/>
+      <c r="F17"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0" pivotTables="0" selectUnlockedCells="1"/>

--- a/2/RATTRAPAGES/notes.xlsx
+++ b/2/RATTRAPAGES/notes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ESIPE\2\RATTRAPAGES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162C6A19-F429-4A18-B89B-162458BAB6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7697E60D-BE1B-45EE-8A6A-558DA841BA8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
